--- a/Problem3_Expected_Credit_Loss_IFRS9_CECL/reports/financial_impact_reporting_packaging/AMEX_Problem3_Financial_Impact_Workbook.xlsx
+++ b/Problem3_Expected_Credit_Loss_IFRS9_CECL/reports/financial_impact_reporting_packaging/AMEX_Problem3_Financial_Impact_Workbook.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -125,18 +131,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -147,15 +153,30 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -817,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -827,6 +848,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -841,13 +863,20 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Total ECL -- Flat LGD (Notebook 08)</t>
         </is>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="18">
         <f>'Standard Comparison'!B2</f>
         <v/>
       </c>
@@ -858,7 +887,7 @@
           <t>Total ECL -- IFRS9 Staged</t>
         </is>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="18">
         <f>'Standard Comparison'!B3</f>
         <v/>
       </c>
@@ -869,7 +898,7 @@
           <t>Total ECL -- CECL Lifetime</t>
         </is>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="18">
         <f>'Standard Comparison'!B4</f>
         <v/>
       </c>
@@ -880,7 +909,7 @@
           <t>Reserve Change (IFRS9 - Flat)</t>
         </is>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="19">
         <f>D6-D5</f>
         <v/>
       </c>
@@ -891,7 +920,7 @@
           <t>CECL Day-One Delta (CECL - IFRS9)</t>
         </is>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="19">
         <f>D7-D6</f>
         <v/>
       </c>
@@ -902,7 +931,7 @@
           <t>Recommended Stress Buffer</t>
         </is>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="20">
         <f>'Macro Sensitivity'!G2</f>
         <v/>
       </c>
@@ -1005,7 +1034,7 @@
           <t>Ead Per Account Usd</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="21" t="n">
         <v>5000</v>
       </c>
       <c r="C2" s="12" t="inlineStr">
@@ -1020,7 +1049,7 @@
           <t>Baseline Flat Lgd</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="22" t="n">
         <v>0.45</v>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -1050,7 +1079,7 @@
           <t>Analyst Hourly Cost Usd</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="21" t="n">
         <v>100</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1065,7 +1094,7 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="21" t="n">
         <v>70000</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1134,10 +1163,10 @@
           <t>Notebook 08: Basel/IFRS9, flat 45% LGD, outcome-based Stage 3</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B2" s="23" t="n">
         <v>67830905.87</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="23">
         <f>B2-$B$2</f>
         <v/>
       </c>
@@ -1148,10 +1177,10 @@
           <t>Notebook 31: IFRS9 staged, tier-LGD, outcome-free staging</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="23" t="n">
         <v>72448498.95</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="23">
         <f>B3-$B$2</f>
         <v/>
       </c>
@@ -1162,10 +1191,10 @@
           <t>Notebook 31: CECL lifetime-for-all, tier-LGD, no staging</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="23" t="n">
         <v>73051922.56999999</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="23">
         <f>B4-$B$2</f>
         <v/>
       </c>
@@ -1236,13 +1265,13 @@
           <t>Upside</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="24" t="n">
         <v>0.2</v>
       </c>
       <c r="C2" t="n">
         <v>0.85</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="23" t="n">
         <v>62509011.41</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -1250,7 +1279,7 @@
           <t>Stress Buffer (Downside - Baseline)</t>
         </is>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="25">
         <f>D4-D3</f>
         <v/>
       </c>
@@ -1261,13 +1290,13 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="24" t="n">
         <v>0.5</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="23" t="n">
         <v>73540013.42</v>
       </c>
     </row>
@@ -1277,13 +1306,13 @@
           <t>Downside</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="24" t="n">
         <v>0.3</v>
       </c>
       <c r="C4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="23" t="n">
         <v>77255633.18000001</v>
       </c>
     </row>
